--- a/final_runs/RQ2_uq_hallucination_detection/single_metric_table.xlsx
+++ b/final_runs/RQ2_uq_hallucination_detection/single_metric_table.xlsx
@@ -12897,7 +12897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-11T15:43:00.622291</t>
+          <t>2026-01-12T17:12:09.738572</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
